--- a/courses/blackbelt-agentic-abm/module-4-abm-metrics/kpi-workbook.xlsx
+++ b/courses/blackbelt-agentic-abm/module-4-abm-metrics/kpi-workbook.xlsx
@@ -1096,7 +1096,7 @@
     <row r="47">
       <c r="B47" s="18" t="inlineStr">
         <is>
-          <t>Adapted from a training originally delivered in Russian; illustrative figures only. See the Module 4 notes page for the worked JLL case study and definitions of each metric.</t>
+          <t>Illustrative figures only. See the Module 4 notes page for the worked JLL case study and definitions of each metric.</t>
         </is>
       </c>
     </row>
